--- a/docs/v3.0.0-preview1/StructureDefinition-VRM-AliasParameters.xlsx
+++ b/docs/v3.0.0-preview1/StructureDefinition-VRM-AliasParameters.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-09T11:35:05-04:00</t>
+    <t>2025-08-11T15:01:09-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1221,15 +1221,15 @@
   <dimension ref="A1:AL110"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.11328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="32.28515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="23.23046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="17.796875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="34.31640625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="25.0703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="18.70703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1240,24 +1240,24 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.2265625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="48.90234375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="28.8359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="68.13671875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="50.9296875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="30.5546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="22.2109375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="19.5625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="22.43359375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="20.3359375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/v3.0.0-preview1/StructureDefinition-VRM-AliasParameters.xlsx
+++ b/docs/v3.0.0-preview1/StructureDefinition-VRM-AliasParameters.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-11T15:01:09-04:00</t>
+    <t>2025-11-25T14:04:25-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -348,7 +348,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>

--- a/docs/v3.0.0-preview1/StructureDefinition-VRM-AliasParameters.xlsx
+++ b/docs/v3.0.0-preview1/StructureDefinition-VRM-AliasParameters.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3739" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3739" uniqueCount="296">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T14:04:25-05:00</t>
+    <t>2026-03-24T12:23:49-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -348,13 +348,16 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
   </si>
   <si>
     <t>Parameters.parameter</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t xml:space="preserve">BackboneElement
@@ -622,7 +625,7 @@
     <t>event_year</t>
   </si>
   <si>
-    <t>DOD_YR or DOB_YR or FDOD_YR event year</t>
+    <t>DOD_YR or IDOB_YR or FDOD_YR event year</t>
   </si>
   <si>
     <t>four digit event year</t>
@@ -1927,7 +1930,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>76</v>
@@ -1942,13 +1945,13 @@
         <v>84</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1987,16 +1990,16 @@
         <v>20</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AF7" t="s" s="2">
         <v>111</v>
@@ -2011,7 +2014,7 @@
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -2022,10 +2025,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2048,13 +2051,13 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -2105,7 +2108,7 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>75</v>
@@ -2128,14 +2131,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2154,16 +2157,16 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2213,7 +2216,7 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
@@ -2225,7 +2228,7 @@
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2236,14 +2239,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2262,19 +2265,19 @@
         <v>84</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>20</v>
@@ -2323,7 +2326,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
@@ -2335,21 +2338,21 @@
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2372,13 +2375,13 @@
         <v>84</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2429,7 +2432,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>83</v>
@@ -2452,10 +2455,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2478,13 +2481,13 @@
         <v>84</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2535,7 +2538,7 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2544,7 +2547,7 @@
         <v>83</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>95</v>
@@ -2558,10 +2561,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2584,16 +2587,16 @@
         <v>84</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2643,16 +2646,16 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI13" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>20</v>
@@ -2666,10 +2669,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2695,13 +2698,13 @@
         <v>77</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2751,7 +2754,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2774,20 +2777,20 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>111</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>83</v>
@@ -2802,13 +2805,13 @@
         <v>84</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2871,7 +2874,7 @@
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
@@ -2882,10 +2885,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2908,13 +2911,13 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2965,7 +2968,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -2988,10 +2991,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3014,13 +3017,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3071,7 +3074,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -3083,7 +3086,7 @@
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
@@ -3094,14 +3097,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3120,19 +3123,19 @@
         <v>84</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3181,7 +3184,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -3193,21 +3196,21 @@
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3230,13 +3233,13 @@
         <v>84</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3248,7 +3251,7 @@
         <v>20</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>20</v>
@@ -3287,7 +3290,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>83</v>
@@ -3310,10 +3313,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3336,13 +3339,13 @@
         <v>84</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3369,11 +3372,11 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -3391,7 +3394,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -3400,7 +3403,7 @@
         <v>83</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>95</v>
@@ -3414,10 +3417,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3440,16 +3443,16 @@
         <v>84</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3499,16 +3502,16 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI21" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>20</v>
@@ -3522,10 +3525,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3551,13 +3554,13 @@
         <v>20</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3607,7 +3610,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -3630,13 +3633,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>111</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>20</v>
@@ -3658,13 +3661,13 @@
         <v>84</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3727,7 +3730,7 @@
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
@@ -3738,10 +3741,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3764,13 +3767,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3821,7 +3824,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -3844,10 +3847,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3870,13 +3873,13 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3927,7 +3930,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -3939,7 +3942,7 @@
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -3950,14 +3953,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -3976,19 +3979,19 @@
         <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4037,7 +4040,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -4049,21 +4052,21 @@
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4086,13 +4089,13 @@
         <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4104,7 +4107,7 @@
         <v>20</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>20</v>
@@ -4143,7 +4146,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
@@ -4166,10 +4169,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4192,13 +4195,13 @@
         <v>84</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4249,7 +4252,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -4258,7 +4261,7 @@
         <v>83</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>95</v>
@@ -4272,10 +4275,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4298,16 +4301,16 @@
         <v>84</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4357,16 +4360,16 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI29" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="AG29" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>20</v>
@@ -4380,10 +4383,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4409,13 +4412,13 @@
         <v>20</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4465,7 +4468,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -4488,13 +4491,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>111</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>20</v>
@@ -4516,13 +4519,13 @@
         <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4585,7 +4588,7 @@
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -4596,10 +4599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4622,13 +4625,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4679,7 +4682,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -4702,10 +4705,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4728,13 +4731,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4785,7 +4788,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -4797,7 +4800,7 @@
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -4808,14 +4811,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -4834,19 +4837,19 @@
         <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -4895,7 +4898,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -4907,21 +4910,21 @@
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4944,13 +4947,13 @@
         <v>84</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4962,7 +4965,7 @@
         <v>20</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>20</v>
@@ -5001,7 +5004,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -5024,10 +5027,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5050,13 +5053,13 @@
         <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5107,7 +5110,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -5116,7 +5119,7 @@
         <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>95</v>
@@ -5130,10 +5133,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5156,16 +5159,16 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5215,16 +5218,16 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI37" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>20</v>
@@ -5238,10 +5241,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5267,13 +5270,13 @@
         <v>20</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5323,7 +5326,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
@@ -5346,13 +5349,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>111</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>20</v>
@@ -5374,13 +5377,13 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5443,7 +5446,7 @@
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -5454,10 +5457,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5480,13 +5483,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5537,7 +5540,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -5560,10 +5563,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5586,13 +5589,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5643,7 +5646,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -5655,7 +5658,7 @@
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -5666,14 +5669,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -5692,19 +5695,19 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -5753,7 +5756,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
@@ -5765,21 +5768,21 @@
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5802,13 +5805,13 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5820,7 +5823,7 @@
         <v>20</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>20</v>
@@ -5859,7 +5862,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -5882,10 +5885,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5908,13 +5911,13 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5965,7 +5968,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -5974,7 +5977,7 @@
         <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>95</v>
@@ -5988,10 +5991,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6014,16 +6017,16 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6073,16 +6076,16 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI45" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>20</v>
@@ -6096,10 +6099,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6125,13 +6128,13 @@
         <v>20</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6181,7 +6184,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
@@ -6204,13 +6207,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>111</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>20</v>
@@ -6232,13 +6235,13 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6301,7 +6304,7 @@
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -6312,10 +6315,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6338,13 +6341,13 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6395,7 +6398,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
@@ -6418,10 +6421,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6444,13 +6447,13 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6501,7 +6504,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
@@ -6513,7 +6516,7 @@
         <v>20</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>20</v>
@@ -6524,14 +6527,14 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6550,19 +6553,19 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -6611,7 +6614,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -6623,21 +6626,21 @@
         <v>20</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6660,13 +6663,13 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6678,7 +6681,7 @@
         <v>20</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>20</v>
@@ -6717,7 +6720,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -6740,10 +6743,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6766,13 +6769,13 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6823,7 +6826,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
@@ -6832,7 +6835,7 @@
         <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>95</v>
@@ -6846,10 +6849,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6872,16 +6875,16 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -6931,16 +6934,16 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI53" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>20</v>
@@ -6954,10 +6957,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6983,13 +6986,13 @@
         <v>20</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7039,7 +7042,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
@@ -7062,13 +7065,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>111</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>20</v>
@@ -7090,13 +7093,13 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7159,7 +7162,7 @@
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
@@ -7170,10 +7173,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7196,13 +7199,13 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7253,7 +7256,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -7276,10 +7279,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7302,13 +7305,13 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7359,7 +7362,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -7371,7 +7374,7 @@
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
@@ -7382,14 +7385,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7408,19 +7411,19 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -7469,7 +7472,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
@@ -7481,21 +7484,21 @@
         <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7518,13 +7521,13 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7536,7 +7539,7 @@
         <v>20</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>20</v>
@@ -7575,7 +7578,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -7598,10 +7601,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7624,13 +7627,13 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7657,11 +7660,11 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -7679,7 +7682,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
@@ -7688,7 +7691,7 @@
         <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>95</v>
@@ -7702,10 +7705,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7728,16 +7731,16 @@
         <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7787,16 +7790,16 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI61" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>20</v>
@@ -7810,10 +7813,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7839,13 +7842,13 @@
         <v>20</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -7895,7 +7898,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
@@ -7918,13 +7921,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>111</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>20</v>
@@ -7946,13 +7949,13 @@
         <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8015,7 +8018,7 @@
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
@@ -8026,10 +8029,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8052,13 +8055,13 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8109,7 +8112,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
@@ -8132,10 +8135,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8158,13 +8161,13 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8215,7 +8218,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
@@ -8227,7 +8230,7 @@
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
@@ -8238,14 +8241,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -8264,19 +8267,19 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -8325,7 +8328,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
@@ -8337,21 +8340,21 @@
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8374,13 +8377,13 @@
         <v>84</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8392,7 +8395,7 @@
         <v>20</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>20</v>
@@ -8431,7 +8434,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -8454,10 +8457,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8480,13 +8483,13 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8537,7 +8540,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>75</v>
@@ -8546,7 +8549,7 @@
         <v>83</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>95</v>
@@ -8560,10 +8563,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8586,16 +8589,16 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8645,16 +8648,16 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI69" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>20</v>
@@ -8668,10 +8671,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8697,13 +8700,13 @@
         <v>20</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -8753,7 +8756,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -8776,13 +8779,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>111</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>20</v>
@@ -8804,13 +8807,13 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8873,7 +8876,7 @@
         <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>20</v>
@@ -8884,10 +8887,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8910,13 +8913,13 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8967,7 +8970,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
@@ -8990,10 +8993,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9016,13 +9019,13 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9073,7 +9076,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
@@ -9085,7 +9088,7 @@
         <v>20</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>20</v>
@@ -9096,14 +9099,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9122,19 +9125,19 @@
         <v>84</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -9183,7 +9186,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>75</v>
@@ -9195,21 +9198,21 @@
         <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9232,13 +9235,13 @@
         <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9250,7 +9253,7 @@
         <v>20</v>
       </c>
       <c r="S75" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="T75" t="s" s="2">
         <v>20</v>
@@ -9289,7 +9292,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -9312,10 +9315,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9338,13 +9341,13 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9395,7 +9398,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>75</v>
@@ -9404,7 +9407,7 @@
         <v>83</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>95</v>
@@ -9418,10 +9421,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9444,16 +9447,16 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -9503,16 +9506,16 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI77" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>20</v>
@@ -9526,10 +9529,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9555,13 +9558,13 @@
         <v>20</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -9611,7 +9614,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
@@ -9634,13 +9637,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>111</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>20</v>
@@ -9662,13 +9665,13 @@
         <v>84</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9731,7 +9734,7 @@
         <v>20</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>20</v>
@@ -9742,10 +9745,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9768,13 +9771,13 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9825,7 +9828,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>75</v>
@@ -9848,10 +9851,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9874,13 +9877,13 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9931,7 +9934,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>75</v>
@@ -9943,7 +9946,7 @@
         <v>20</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>20</v>
@@ -9954,14 +9957,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -9980,19 +9983,19 @@
         <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -10041,7 +10044,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>75</v>
@@ -10053,21 +10056,21 @@
         <v>20</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10090,13 +10093,13 @@
         <v>84</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -10108,7 +10111,7 @@
         <v>20</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>20</v>
@@ -10147,7 +10150,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
@@ -10170,10 +10173,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10196,13 +10199,13 @@
         <v>84</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10253,7 +10256,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>75</v>
@@ -10262,7 +10265,7 @@
         <v>83</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>95</v>
@@ -10276,10 +10279,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10302,16 +10305,16 @@
         <v>84</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -10361,16 +10364,16 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI85" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>20</v>
@@ -10384,10 +10387,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10413,13 +10416,13 @@
         <v>20</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10469,7 +10472,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>75</v>
@@ -10492,13 +10495,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>111</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>20</v>
@@ -10520,13 +10523,13 @@
         <v>84</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10589,7 +10592,7 @@
         <v>20</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>20</v>
@@ -10600,10 +10603,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10626,13 +10629,13 @@
         <v>20</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10683,7 +10686,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>75</v>
@@ -10706,10 +10709,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10732,13 +10735,13 @@
         <v>20</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10789,7 +10792,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
@@ -10801,7 +10804,7 @@
         <v>20</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>20</v>
@@ -10812,14 +10815,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -10838,19 +10841,19 @@
         <v>84</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -10899,7 +10902,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>75</v>
@@ -10911,21 +10914,21 @@
         <v>20</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10948,13 +10951,13 @@
         <v>84</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -10966,7 +10969,7 @@
         <v>20</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>20</v>
@@ -11005,7 +11008,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -11028,10 +11031,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11054,13 +11057,13 @@
         <v>84</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -11111,7 +11114,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>75</v>
@@ -11120,7 +11123,7 @@
         <v>83</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>95</v>
@@ -11134,10 +11137,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11160,16 +11163,16 @@
         <v>84</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -11219,16 +11222,16 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI93" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>20</v>
@@ -11242,10 +11245,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11271,13 +11274,13 @@
         <v>20</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -11327,7 +11330,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>
@@ -11350,13 +11353,13 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>111</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>20</v>
@@ -11378,13 +11381,13 @@
         <v>84</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11447,7 +11450,7 @@
         <v>20</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>20</v>
@@ -11458,10 +11461,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11484,13 +11487,13 @@
         <v>20</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -11541,7 +11544,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>75</v>
@@ -11564,10 +11567,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11590,13 +11593,13 @@
         <v>20</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11647,7 +11650,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>75</v>
@@ -11659,7 +11662,7 @@
         <v>20</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>20</v>
@@ -11670,14 +11673,14 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -11696,19 +11699,19 @@
         <v>84</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>20</v>
@@ -11757,7 +11760,7 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>75</v>
@@ -11769,21 +11772,21 @@
         <v>20</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11806,13 +11809,13 @@
         <v>84</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11824,7 +11827,7 @@
         <v>20</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>20</v>
@@ -11863,7 +11866,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>83</v>
@@ -11886,10 +11889,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11912,13 +11915,13 @@
         <v>84</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -11969,7 +11972,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>75</v>
@@ -11978,7 +11981,7 @@
         <v>83</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>95</v>
@@ -11992,10 +11995,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12018,16 +12021,16 @@
         <v>84</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -12077,16 +12080,16 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI101" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>20</v>
@@ -12100,10 +12103,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12129,13 +12132,13 @@
         <v>20</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -12185,7 +12188,7 @@
         <v>20</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>75</v>
@@ -12208,13 +12211,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>111</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>20</v>
@@ -12236,13 +12239,13 @@
         <v>84</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -12305,7 +12308,7 @@
         <v>20</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>20</v>
@@ -12316,10 +12319,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12342,13 +12345,13 @@
         <v>20</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -12399,7 +12402,7 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>75</v>
@@ -12422,10 +12425,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12448,13 +12451,13 @@
         <v>20</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12505,7 +12508,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>75</v>
@@ -12517,7 +12520,7 @@
         <v>20</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>20</v>
@@ -12528,14 +12531,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -12554,19 +12557,19 @@
         <v>84</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>20</v>
@@ -12615,7 +12618,7 @@
         <v>20</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>75</v>
@@ -12627,21 +12630,21 @@
         <v>20</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12664,13 +12667,13 @@
         <v>84</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -12682,7 +12685,7 @@
         <v>20</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>20</v>
@@ -12721,7 +12724,7 @@
         <v>20</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>83</v>
@@ -12744,10 +12747,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12770,13 +12773,13 @@
         <v>84</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -12827,7 +12830,7 @@
         <v>20</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>75</v>
@@ -12836,7 +12839,7 @@
         <v>83</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>95</v>
@@ -12850,10 +12853,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12876,16 +12879,16 @@
         <v>84</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -12935,16 +12938,16 @@
         <v>20</v>
       </c>
       <c r="AF109" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI109" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>20</v>
@@ -12958,10 +12961,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12987,13 +12990,13 @@
         <v>20</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13043,7 +13046,7 @@
         <v>20</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>75</v>
